--- a/results/job_matches_2026-05-27.xlsx
+++ b/results/job_matches_2026-05-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>Modem Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=960f767365c3fdc0</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3f6235da80ec1d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Quarterhill</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ab23efc926ec48</t>
+          <t>https://www.indeed.com/viewjob?jk=960f767365c3fdc0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior AWS Cloud Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01264aaa08f1855</t>
+          <t>https://www.indeed.com/viewjob?jk=45e2e8c07008edb9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026012 - Senior Software Analyst</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>Quarterhill</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59907092ed75df82</t>
+          <t>https://www.indeed.com/viewjob?jk=87ab23efc926ec48</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Quarterhill</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b056aa8ae1df1b</t>
+          <t>https://www.indeed.com/viewjob?jk=b01264aaa08f1855</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Infrastructure Engineering Senior Advisor- Hybrid</t>
+          <t>2026012 - Senior Software Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1b08ac884b7ab5</t>
+          <t>https://www.indeed.com/viewjob?jk=59907092ed75df82</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Quarterhill</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e2e8c07008edb9</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b056aa8ae1df1b</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Copy of Senior Data Engineer (Azure &amp; Databricks)</t>
+          <t>AWS Data Engineer (Cloud Data Platform &amp; Pipeline Specialist) (FTE / Onsite)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=634ea8c9beab0812</t>
+          <t>https://www.indeed.com/viewjob?jk=2feefef0c932976c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure &amp; Databricks)</t>
+          <t>Copy of Senior Data Engineer (Azure &amp; Databricks)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd215d5414c53bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=634ea8c9beab0812</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Emerging Technologies (AI, GenAI, ML)</t>
+          <t>Senior Data Engineer (Azure &amp; Databricks)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Empower</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Vertex AI, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21e1b2180a79f7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=dd215d5414c53bc0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Architecture Senior Advisor</t>
+          <t>Senior Solutions Architect - Emerging Technologies (AI, GenAI, ML)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Empower</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, ECS, Azure, Vertex AI, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd686e8a6d93c00</t>
+          <t>https://www.indeed.com/viewjob?jk=21e1b2180a79f7cc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Architecture Senior Advisor</t>
+          <t>Senior Full Stack Software Engineer - Catalogs, Hierarchy &amp; OrgMDM (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Kafka, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a100c3ae58674b37</t>
+          <t>https://www.indeed.com/viewjob?jk=83f82aaa0bacb5b1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Architecture Senior Advisor</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Prime Cargo People Logistics</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, GCP, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Redshift, ECS, RDS, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c504b34cabd6342d</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd686e8a6d93c00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer II - Surgery</t>
+          <t>Architecture Senior Advisor</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, ECS, RDS, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443f2bd8cdbdcd91</t>
+          <t>https://www.indeed.com/viewjob?jk=a100c3ae58674b37</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Engineer 2: AI Agentic Solutions (Hybrid - Seattle, WA)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Prime Cargo People Logistics</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, GCP, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1942d9ec58e935c</t>
+          <t>https://www.indeed.com/viewjob?jk=c504b34cabd6342d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer II - Surgery</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Macmillan Publishers</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb1d2668d2c3bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=443f2bd8cdbdcd91</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer 2: AI Agentic Solutions (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Specialized Dental</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Medallion Architecture, Scala, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97619fb277569f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=d1942d9ec58e935c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack AI + Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Techtorch</t>
+          <t>Macmillan Publishers</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Spark Streaming, Kafka, PostgreSQL, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6740052e5af1c2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb1d2668d2c3bb3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026011 - Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>Specialized Dental</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Data Factory, Medallion Architecture, Scala, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21cc17fa6fcb98f8</t>
+          <t>https://www.indeed.com/viewjob?jk=97619fb277569f5d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>Full Stack AI + Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>Techtorch</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Azure, Spark, Spark Streaming, Kafka, PostgreSQL, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2be82c2c579e7f0</t>
+          <t>https://www.indeed.com/viewjob?jk=6740052e5af1c2fe</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>2026011 - Operations Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Dask, NoSQL, MLOps, MLflow, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3462d2e2223e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=21cc17fa6fcb98f8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1985124aab93f8b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4df4e36af097a7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Infrastructure Engineering Senior Advisor- Hybrid</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a56f4caf667cc4a</t>
+          <t>https://www.indeed.com/viewjob?jk=c2be82c2c579e7f0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Dask, NoSQL, MLOps, MLflow, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8cd3096eac30881</t>
+          <t>https://www.indeed.com/viewjob?jk=be3462d2e2223e8d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Butler Till</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50977d506f8a126</t>
+          <t>https://www.indeed.com/viewjob?jk=1985124aab93f8b5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Acquire-Site Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BehaviorSpan</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a716d21991893978</t>
+          <t>https://www.indeed.com/viewjob?jk=f8cd3096eac30881</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Always Compassionate Health</t>
+          <t>Butler Till</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e602a7ae37682d44</t>
+          <t>https://www.indeed.com/viewjob?jk=b50977d506f8a126</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Snowflake Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=002369ff092a4302</t>
+          <t>https://www.indeed.com/viewjob?jk=78902f746ba9d9e9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Kafka Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Scala, Oracle, DynamoDB, NoSQL, ETL, dbt, Tableau, Git, Bitbucket</t>
+          <t>Azure, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=716c39142598395c</t>
+          <t>https://www.indeed.com/viewjob?jk=cd25b4ca05cd6b8c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kinsale Management Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB, Data Modeling</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a938739108dd1870</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6f76b9337a13b3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Acquire-Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>BehaviorSpan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623ad57a66a94f1a</t>
+          <t>https://www.indeed.com/viewjob?jk=a716d21991893978</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Interra Health</t>
+          <t>Always Compassionate Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dffdb4bf979c0c04</t>
+          <t>https://www.indeed.com/viewjob?jk=e602a7ae37682d44</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer II - Java/Python</t>
+          <t>Snowflake Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e901ac4878117ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=002369ff092a4302</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Newsbreak</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
+          <t>AWS, Scala, Oracle, DynamoDB, NoSQL, ETL, dbt, Tableau, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f967de110027227c</t>
+          <t>https://www.indeed.com/viewjob?jk=716c39142598395c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Newsbreak</t>
+          <t>Kinsale Management Inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea855ad903dd71df</t>
+          <t>https://www.indeed.com/viewjob?jk=a938739108dd1870</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Quanex</t>
+          <t>Enlyte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22e7be74451275b</t>
+          <t>https://www.indeed.com/viewjob?jk=623ad57a66a94f1a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Interra Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, CI/CD, Airflow</t>
+          <t>RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877d45e3d1a625d6</t>
+          <t>https://www.indeed.com/viewjob?jk=dffdb4bf979c0c04</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Cloud Data Platform</t>
+          <t>Software Engineer II - Java/Python</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Informatica PowerCenter, Data Modeling, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de80a4e1ea3c7456</t>
+          <t>https://www.indeed.com/viewjob?jk=e901ac4878117ce6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed Engineer - QuantumBlack, AI by McKinsey</t>
+          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Newsbreak</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99421b7cddeacb9e</t>
+          <t>https://www.indeed.com/viewjob?jk=f967de110027227c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, App</t>
+          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Newsbreak</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca392fa39b84631e</t>
+          <t>https://www.indeed.com/viewjob?jk=ea855ad903dd71df</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, App</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Quanex</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f024bf694f893ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=f22e7be74451275b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MuleSoft/Python Software Engineer - OIT</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Emory University</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,19 +2491,19 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a511e772aaa75c08</t>
+          <t>https://www.indeed.com/viewjob?jk=877d45e3d1a625d6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Data Architect</t>
+          <t>Senior Data Engineer - Cloud Data Platform</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>YETI</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Vertex AI, Scala, Databricks Lakehouse</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Informatica PowerCenter, Data Modeling, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c9a108f2d63b6a3</t>
+          <t>https://www.indeed.com/viewjob?jk=de80a4e1ea3c7456</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Architect – Manufacturing Test</t>
+          <t>Senior Forward Deployed Engineer - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cerebras Systems</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c04a9f371533f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=99421b7cddeacb9e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Engineer, Software Automation Test Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Spectra Logic</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b0e0a0263f945e7</t>
+          <t>https://www.indeed.com/viewjob?jk=5cf30157db81ea0e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Architect – Manufacturing Test</t>
+          <t>Senior Software Engineer, App</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cerebras Systems</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ec3a8e9018054</t>
+          <t>https://www.indeed.com/viewjob?jk=ca392fa39b84631e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer, App</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cf30157db81ea0e</t>
+          <t>https://www.indeed.com/viewjob?jk=f024bf694f893ebe</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Security Engineer - Vuln Management (Infra)</t>
+          <t>MuleSoft/Python Software Engineer - OIT</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Replit</t>
+          <t>Emory University</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, S3, IAM, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f8e63a431463bc</t>
+          <t>https://www.indeed.com/viewjob?jk=a511e772aaa75c08</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Sr. Data Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>YETI</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Vertex AI, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed909357965ec568</t>
+          <t>https://www.indeed.com/viewjob?jk=6c9a108f2d63b6a3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Software Architect – Manufacturing Test</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Cerebras Systems</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a49347bb46652a75</t>
+          <t>https://www.indeed.com/viewjob?jk=1c04a9f371533f2c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Engineer, Software Automation Test Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Spectra Logic</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b8a567bdd35f252</t>
+          <t>https://www.indeed.com/viewjob?jk=9b0e0a0263f945e7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Architect – Manufacturing Test</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Cerebras Systems</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e70cddc4d406c6fc</t>
+          <t>https://www.indeed.com/viewjob?jk=132ec3a8e9018054</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Security Engineer - Vuln Management (Infra)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nexstar Media Group, Inc.</t>
+          <t>Replit</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b532541851ceb06</t>
+          <t>https://www.indeed.com/viewjob?jk=06f8e63a431463bc</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes, CloudWatch</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ee880f838d01800</t>
+          <t>https://www.indeed.com/viewjob?jk=ed909357965ec568</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b975973860fe466c</t>
+          <t>https://www.indeed.com/viewjob?jk=a49347bb46652a75</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,15 +2971,190 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b8a567bdd35f252</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e70cddc4d406c6fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Nexstar Media Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b532541851ceb06</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Recutify Inc.</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ee880f838d01800</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Lila Sciences</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
           <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b975973860fe466c</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Lila Sciences</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b47adc71ffc989c2</t>
         </is>

--- a/results/job_matches_2026-05-27.xlsx
+++ b/results/job_matches_2026-05-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer, I - Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TORC Robotics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=196506204c7c944f</t>
+          <t>https://www.indeed.com/viewjob?jk=e523bf5a5bf5d62b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Controllers, Software Engineering, Salt Lake City, Associate</t>
+          <t>Software Engineer, I - Data Engineering</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81361a25f18bfa9e</t>
+          <t>https://www.indeed.com/viewjob?jk=196506204c7c944f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BI Solutions Architect</t>
+          <t>Controllers, Software Engineering, Salt Lake City, Associate</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mars Technominds</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa071bc6a31ae41</t>
+          <t>https://www.indeed.com/viewjob?jk=81361a25f18bfa9e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>BI Solutions Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mars Technominds</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b965cc65d75bb68</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa071bc6a31ae41</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Architect/Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rockwell Automation</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Polars, PostgreSQL, Azure Cosmos DB, NoSQL, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc83cb585d053a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=4b965cc65d75bb68</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III, Voice AI</t>
+          <t>Senior Agentic AI Architect/Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Natera</t>
+          <t>Rockwell Automation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Azure, Scala, Kafka</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Polars, PostgreSQL, Azure Cosmos DB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff57ba86e213734</t>
+          <t>https://www.indeed.com/viewjob?jk=cc83cb585d053a0f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Modem Machine Learning Engineer</t>
+          <t>Software Engineer III, Voice AI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Natera</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Azure, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3f6235da80ec1d</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff57ba86e213734</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>Modem Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,42 +1056,42 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=960f767365c3fdc0</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3f6235da80ec1d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Developer</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e2e8c07008edb9</t>
+          <t>https://www.indeed.com/viewjob?jk=960f767365c3fdc0</t>
         </is>
       </c>
     </row>
@@ -1238,87 +1238,87 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Allruva Technology Services</t>
+          <t>Bessemer Trust</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, HDFS, Hive, MapReduce, HBase, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3fc6d4b0669cc2e</t>
+          <t>https://www.indeed.com/viewjob?jk=774b596dfb394ced</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS Data Engineer (Cloud Data Platform &amp; Pipeline Specialist) (FTE / Onsite)</t>
+          <t>Senior AWS Cloud Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2feefef0c932976c</t>
+          <t>https://www.indeed.com/viewjob?jk=45e2e8c07008edb9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Copy of Senior Data Engineer (Azure &amp; Databricks)</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Allruva Technology Services</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>RDS, Databricks, Hadoop, HDFS, Hive, MapReduce, HBase, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=634ea8c9beab0812</t>
+          <t>https://www.indeed.com/viewjob?jk=a3fc6d4b0669cc2e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure &amp; Databricks)</t>
+          <t>AWS Data Engineer (Cloud Data Platform &amp; Pipeline Specialist) (FTE / Onsite)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd215d5414c53bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=2feefef0c932976c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Emerging Technologies (AI, GenAI, ML)</t>
+          <t>Copy of Senior Data Engineer (Azure &amp; Databricks)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Empower</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Vertex AI, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21e1b2180a79f7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=634ea8c9beab0812</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer - Catalogs, Hierarchy &amp; OrgMDM (Hybrid - Seattle, WA)</t>
+          <t>Senior Data Engineer (Azure &amp; Databricks)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Kafka, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f82aaa0bacb5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=dd215d5414c53bc0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Architecture Senior Advisor</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd686e8a6d93c00</t>
+          <t>https://www.indeed.com/viewjob?jk=1985124aab93f8b5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Architecture Senior Advisor</t>
+          <t>Senior Solutions Architect - Emerging Technologies (AI, GenAI, ML)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Empower</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, ECS, Azure, Vertex AI, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a100c3ae58674b37</t>
+          <t>https://www.indeed.com/viewjob?jk=21e1b2180a79f7cc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Full Stack Software Engineer - Catalogs, Hierarchy &amp; OrgMDM (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Prime Cargo People Logistics</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, GCP, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Kafka, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c504b34cabd6342d</t>
+          <t>https://www.indeed.com/viewjob?jk=83f82aaa0bacb5b1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer II - Surgery</t>
+          <t>Architecture Senior Advisor</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, ECS, RDS, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443f2bd8cdbdcd91</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd686e8a6d93c00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Engineer 2: AI Agentic Solutions (Hybrid - Seattle, WA)</t>
+          <t>Architecture Senior Advisor</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Redshift, ECS, RDS, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,19 +1616,19 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1942d9ec58e935c</t>
+          <t>https://www.indeed.com/viewjob?jk=a100c3ae58674b37</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Macmillan Publishers</t>
+          <t>Prime Cargo People Logistics</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1637,11 +1637,11 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, RDS, GCP, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb1d2668d2c3bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=c504b34cabd6342d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Specialized Dental</t>
+          <t>Holtzbrinck Publishing Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,29 +1676,29 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Medallion Architecture, Scala, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97619fb277569f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=6553fe8d88b5cc2c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack AI + Data Engineer</t>
+          <t>Data Engineer II - Surgery</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Techtorch</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Spark Streaming, Kafka, PostgreSQL, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6740052e5af1c2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=443f2bd8cdbdcd91</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026011 - Operations Engineer</t>
+          <t>Senior Engineer 2: AI Agentic Solutions (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21cc17fa6fcb98f8</t>
+          <t>https://www.indeed.com/viewjob?jk=d1942d9ec58e935c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Macmillan Publishers</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4df4e36af097a7</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb1d2668d2c3bb3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>Specialized Dental</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Medallion Architecture, Scala, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,19 +1826,19 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2be82c2c579e7f0</t>
+          <t>https://www.indeed.com/viewjob?jk=97619fb277569f5d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Full Stack AI + Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Techtorch</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Dask, NoSQL, MLOps, MLflow, Docker</t>
+          <t>AWS, Azure, Spark, Spark Streaming, Kafka, PostgreSQL, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3462d2e2223e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=6740052e5af1c2fe</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>2026011 - Operations Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1985124aab93f8b5</t>
+          <t>https://www.indeed.com/viewjob?jk=21cc17fa6fcb98f8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8cd3096eac30881</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4df4e36af097a7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Butler Till</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50977d506f8a126</t>
+          <t>https://www.indeed.com/viewjob?jk=c2be82c2c579e7f0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Dask, NoSQL, MLOps, MLflow, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78902f746ba9d9e9</t>
+          <t>https://www.indeed.com/viewjob?jk=be3462d2e2223e8d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kafka Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd25b4ca05cd6b8c</t>
+          <t>https://www.indeed.com/viewjob?jk=f8cd3096eac30881</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Butler Till</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6f76b9337a13b3</t>
+          <t>https://www.indeed.com/viewjob?jk=b50977d506f8a126</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Acquire-Site Reliability Engineer</t>
+          <t>Kafka Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BehaviorSpan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>Azure, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a716d21991893978</t>
+          <t>https://www.indeed.com/viewjob?jk=cd25b4ca05cd6b8c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Always Compassionate Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e602a7ae37682d44</t>
+          <t>https://www.indeed.com/viewjob?jk=78902f746ba9d9e9</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Snowflake Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=002369ff092a4302</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6f76b9337a13b3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Quanex</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Scala, Oracle, DynamoDB, NoSQL, ETL, dbt, Tableau, Git, Bitbucket</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=716c39142598395c</t>
+          <t>https://www.indeed.com/viewjob?jk=f22e7be74451275b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Engineer II, AWS Connect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kinsale Management Inc</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a938739108dd1870</t>
+          <t>https://www.indeed.com/viewjob?jk=3acabec1c779e4f7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Acquire-Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>BehaviorSpan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623ad57a66a94f1a</t>
+          <t>https://www.indeed.com/viewjob?jk=a716d21991893978</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Interra Health</t>
+          <t>Always Compassionate Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dffdb4bf979c0c04</t>
+          <t>https://www.indeed.com/viewjob?jk=e602a7ae37682d44</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer II - Java/Python</t>
+          <t>Snowflake Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,19 +2351,19 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e901ac4878117ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=002369ff092a4302</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Newsbreak</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2372,11 +2372,11 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f967de110027227c</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6ec5c4dd06dea5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Newsbreak</t>
+          <t>Kinsale Management Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea855ad903dd71df</t>
+          <t>https://www.indeed.com/viewjob?jk=a938739108dd1870</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Quanex</t>
+          <t>Enlyte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22e7be74451275b</t>
+          <t>https://www.indeed.com/viewjob?jk=623ad57a66a94f1a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Interra Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, CI/CD, Airflow</t>
+          <t>RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877d45e3d1a625d6</t>
+          <t>https://www.indeed.com/viewjob?jk=dffdb4bf979c0c04</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Cloud Data Platform</t>
+          <t>Software Engineer II - Java/Python</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Informatica PowerCenter, Data Modeling, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de80a4e1ea3c7456</t>
+          <t>https://www.indeed.com/viewjob?jk=e901ac4878117ce6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed Engineer - QuantumBlack, AI by McKinsey</t>
+          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Newsbreak</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99421b7cddeacb9e</t>
+          <t>https://www.indeed.com/viewjob?jk=f967de110027227c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Newsbreak</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Jenkins, Git</t>
+          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cf30157db81ea0e</t>
+          <t>https://www.indeed.com/viewjob?jk=ea855ad903dd71df</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, App</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca392fa39b84631e</t>
+          <t>https://www.indeed.com/viewjob?jk=877d45e3d1a625d6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, App</t>
+          <t>Senior Data Engineer - Cloud Data Platform</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Informatica PowerCenter, Data Modeling, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,19 +2666,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f024bf694f893ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=de80a4e1ea3c7456</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MuleSoft/Python Software Engineer - OIT</t>
+          <t>Senior Forward Deployed Engineer - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Emory University</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a511e772aaa75c08</t>
+          <t>https://www.indeed.com/viewjob?jk=99421b7cddeacb9e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Data Architect</t>
+          <t>Senior Software Engineer, App</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>YETI</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Vertex AI, Scala, Databricks Lakehouse</t>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c9a108f2d63b6a3</t>
+          <t>https://www.indeed.com/viewjob?jk=c5acf07a00ef614c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Architect – Manufacturing Test</t>
+          <t>MuleSoft/Python Software Engineer - OIT</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cerebras Systems</t>
+          <t>Emory University</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, S3, IAM, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c04a9f371533f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=a511e772aaa75c08</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Engineer, Software Automation Test Architect</t>
+          <t>Sr. Data Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Spectra Logic</t>
+          <t>YETI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Vertex AI, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b0e0a0263f945e7</t>
+          <t>https://www.indeed.com/viewjob?jk=6c9a108f2d63b6a3</t>
         </is>
       </c>
     </row>
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ec3a8e9018054</t>
+          <t>https://www.indeed.com/viewjob?jk=1c04a9f371533f2c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Security Engineer - Vuln Management (Infra)</t>
+          <t>Engineer, Software Automation Test Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Replit</t>
+          <t>Spectra Logic</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f8e63a431463bc</t>
+          <t>https://www.indeed.com/viewjob?jk=9b0e0a0263f945e7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Software Architect – Manufacturing Test</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Cerebras Systems</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed909357965ec568</t>
+          <t>https://www.indeed.com/viewjob?jk=132ec3a8e9018054</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Senior Software Engineer, App</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a49347bb46652a75</t>
+          <t>https://www.indeed.com/viewjob?jk=ca392fa39b84631e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer, App</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b8a567bdd35f252</t>
+          <t>https://www.indeed.com/viewjob?jk=f024bf694f893ebe</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Scientist Associate – Product, Experience and Technology (PXT) Analytics Team</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e70cddc4d406c6fc</t>
+          <t>https://www.indeed.com/viewjob?jk=e733ae2cd5148257</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Nexstar Media Group, Inc.</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b532541851ceb06</t>
+          <t>https://www.indeed.com/viewjob?jk=e71383b94e86fbaa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Security Engineer - Vuln Management (Infra)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Replit</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes, CloudWatch</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ee880f838d01800</t>
+          <t>https://www.indeed.com/viewjob?jk=06f8e63a431463bc</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b975973860fe466c</t>
+          <t>https://www.indeed.com/viewjob?jk=ed909357965ec568</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,182 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b47adc71ffc989c2</t>
+          <t>https://www.indeed.com/viewjob?jk=a49347bb46652a75</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cf30157db81ea0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b8a567bdd35f252</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e70cddc4d406c6fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Nexstar Media Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b532541851ceb06</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Recutify Inc.</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ee880f838d01800</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-27.xlsx
+++ b/results/job_matches_2026-05-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,52 +731,52 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Hadoop, HDFS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366df588234a7c92</t>
+          <t>https://www.indeed.com/viewjob?jk=87f70fa8d4be0571</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Solution Architect</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Origence</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8da60d668640f5</t>
+          <t>https://www.indeed.com/viewjob?jk=366df588234a7c92</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Controllers, Software Engineering, Salt Lake City, Associate</t>
+          <t>Full Stack Agentic AI Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,52 +871,52 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81361a25f18bfa9e</t>
+          <t>https://www.indeed.com/viewjob?jk=e6782ecd37a1a284</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BI Solutions Architect</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mars Technominds</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa071bc6a31ae41</t>
+          <t>https://www.indeed.com/viewjob?jk=770d98b3f2c61a3f</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Pr AI Cloud Systems Engineer (RITM0479748)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Quarterhill</t>
+          <t>Discount Tire</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,29 +1116,29 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ab23efc926ec48</t>
+          <t>https://www.indeed.com/viewjob?jk=dc9dfce7125ed878</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01264aaa08f1855</t>
+          <t>https://www.indeed.com/viewjob?jk=fd51c65d58c91761</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026012 - Senior Software Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59907092ed75df82</t>
+          <t>https://www.indeed.com/viewjob?jk=66c6d1fd76fe3448</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Quarterhill</t>
+          <t>Bessemer Trust</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b056aa8ae1df1b</t>
+          <t>https://www.indeed.com/viewjob?jk=774b596dfb394ced</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AWS Cloud Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bessemer Trust</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=774b596dfb394ced</t>
+          <t>https://www.indeed.com/viewjob?jk=45e2e8c07008edb9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Quarterhill</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,42 +1291,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e2e8c07008edb9</t>
+          <t>https://www.indeed.com/viewjob?jk=87ab23efc926ec48</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Allruva Technology Services</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, HDFS, Hive, MapReduce, HBase, Spark, PySpark, Scala</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3fc6d4b0669cc2e</t>
+          <t>https://www.indeed.com/viewjob?jk=b01264aaa08f1855</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AWS Data Engineer (Cloud Data Platform &amp; Pipeline Specialist) (FTE / Onsite)</t>
+          <t>2026012 - Senior Software Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2feefef0c932976c</t>
+          <t>https://www.indeed.com/viewjob?jk=59907092ed75df82</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Copy of Senior Data Engineer (Azure &amp; Databricks)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Quarterhill</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=634ea8c9beab0812</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b056aa8ae1df1b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure &amp; Databricks)</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd215d5414c53bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=a0a72f863d410844</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>Allruva Technology Services</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server</t>
+          <t>RDS, Databricks, Hadoop, HDFS, Hive, MapReduce, HBase, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1985124aab93f8b5</t>
+          <t>https://www.indeed.com/viewjob?jk=a3fc6d4b0669cc2e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Emerging Technologies (AI, GenAI, ML)</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Empower</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Vertex AI, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21e1b2180a79f7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=e62a0487a6b58cf5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer - Catalogs, Hierarchy &amp; OrgMDM (Hybrid - Seattle, WA)</t>
+          <t>Senior Data Engineer (Azure &amp; Databricks)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Kafka, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f82aaa0bacb5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=634ea8c9beab0812</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Architecture Senior Advisor</t>
+          <t>AWS Data Engineer (Cloud Data Platform &amp; Pipeline Specialist) (FTE / Onsite)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd686e8a6d93c00</t>
+          <t>https://www.indeed.com/viewjob?jk=2feefef0c932976c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Architecture Senior Advisor</t>
+          <t>Senior Data Engineer (Azure &amp; Databricks)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a100c3ae58674b37</t>
+          <t>https://www.indeed.com/viewjob?jk=dd215d5414c53bc0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Prime Cargo People Logistics</t>
+          <t>Specialty Building Products</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,77 +1641,77 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, GCP, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c504b34cabd6342d</t>
+          <t>https://www.indeed.com/viewjob?jk=6435e356286a621f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Full Stack Software Engineer - Catalogs, Hierarchy &amp; OrgMDM (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Holtzbrinck Publishing Group</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Kafka, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6553fe8d88b5cc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=83f82aaa0bacb5b1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer II - Surgery</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443f2bd8cdbdcd91</t>
+          <t>https://www.indeed.com/viewjob?jk=1985124aab93f8b5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Engineer 2: AI Agentic Solutions (Hybrid - Seattle, WA)</t>
+          <t>Senior Solutions Architect - Emerging Technologies (AI, GenAI, ML)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Empower</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, ECS, Azure, Vertex AI, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1942d9ec58e935c</t>
+          <t>https://www.indeed.com/viewjob?jk=21e1b2180a79f7cc</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Architecture Senior Advisor</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Macmillan Publishers</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, ECS, RDS, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb1d2668d2c3bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd686e8a6d93c00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Architecture Senior Advisor</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Specialized Dental</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Medallion Architecture, Scala, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, Redshift, ECS, RDS, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97619fb277569f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=a100c3ae58674b37</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack AI + Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Techtorch</t>
+          <t>Prime Cargo People Logistics</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Spark Streaming, Kafka, PostgreSQL, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, ECS, RDS, GCP, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6740052e5af1c2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=c504b34cabd6342d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026011 - Operations Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>Holtzbrinck Publishing Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21cc17fa6fcb98f8</t>
+          <t>https://www.indeed.com/viewjob?jk=6553fe8d88b5cc2c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer II - Surgery</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4df4e36af097a7</t>
+          <t>https://www.indeed.com/viewjob?jk=443f2bd8cdbdcd91</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>Senior Engineer 2: AI Agentic Solutions (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2be82c2c579e7f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d1942d9ec58e935c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Macmillan Publishers</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Dask, NoSQL, MLOps, MLflow, Docker</t>
+          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3462d2e2223e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb1d2668d2c3bb3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack AI + Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Techtorch</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Spark, Spark Streaming, Kafka, PostgreSQL, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8cd3096eac30881</t>
+          <t>https://www.indeed.com/viewjob?jk=6740052e5af1c2fe</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>2026011 - Operations Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Butler Till</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50977d506f8a126</t>
+          <t>https://www.indeed.com/viewjob?jk=21cc17fa6fcb98f8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kafka Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd25b4ca05cd6b8c</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4df4e36af097a7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78902f746ba9d9e9</t>
+          <t>https://www.indeed.com/viewjob?jk=c2be82c2c579e7f0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Dask, NoSQL, MLOps, MLflow, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6f76b9337a13b3</t>
+          <t>https://www.indeed.com/viewjob?jk=be3462d2e2223e8d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Quanex</t>
+          <t>Kinsale Management Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22e7be74451275b</t>
+          <t>https://www.indeed.com/viewjob?jk=a938739108dd1870</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Engineer II, AWS Connect</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Butler Till</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3acabec1c779e4f7</t>
+          <t>https://www.indeed.com/viewjob?jk=b50977d506f8a126</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Acquire-Site Reliability Engineer</t>
+          <t>Kafka Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BehaviorSpan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>Azure, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a716d21991893978</t>
+          <t>https://www.indeed.com/viewjob?jk=cd25b4ca05cd6b8c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Always Compassionate Health</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e602a7ae37682d44</t>
+          <t>https://www.indeed.com/viewjob?jk=f8cd3096eac30881</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Snowflake Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=002369ff092a4302</t>
+          <t>https://www.indeed.com/viewjob?jk=78902f746ba9d9e9</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6ec5c4dd06dea5</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6f76b9337a13b3</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Engineer II, AWS Connect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Kinsale Management Inc</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a938739108dd1870</t>
+          <t>https://www.indeed.com/viewjob?jk=3acabec1c779e4f7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Acquire-Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>BehaviorSpan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623ad57a66a94f1a</t>
+          <t>https://www.indeed.com/viewjob?jk=a716d21991893978</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Interra Health</t>
+          <t>Always Compassionate Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dffdb4bf979c0c04</t>
+          <t>https://www.indeed.com/viewjob?jk=e602a7ae37682d44</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer II - Java/Python</t>
+          <t>Snowflake Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,19 +2526,19 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e901ac4878117ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=002369ff092a4302</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Newsbreak</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2547,11 +2547,11 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f967de110027227c</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6ec5c4dd06dea5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Newsbreak</t>
+          <t>Enlyte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea855ad903dd71df</t>
+          <t>https://www.indeed.com/viewjob?jk=623ad57a66a94f1a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Interra Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, CI/CD, Airflow</t>
+          <t>RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877d45e3d1a625d6</t>
+          <t>https://www.indeed.com/viewjob?jk=dffdb4bf979c0c04</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Cloud Data Platform</t>
+          <t>Software Engineer II - Java/Python</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Informatica PowerCenter, Data Modeling, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de80a4e1ea3c7456</t>
+          <t>https://www.indeed.com/viewjob?jk=e901ac4878117ce6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed Engineer - QuantumBlack, AI by McKinsey</t>
+          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Newsbreak</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99421b7cddeacb9e</t>
+          <t>https://www.indeed.com/viewjob?jk=f967de110027227c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, App</t>
+          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Newsbreak</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5acf07a00ef614c</t>
+          <t>https://www.indeed.com/viewjob?jk=ea855ad903dd71df</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MuleSoft/Python Software Engineer - OIT</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Emory University</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,19 +2771,19 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a511e772aaa75c08</t>
+          <t>https://www.indeed.com/viewjob?jk=877d45e3d1a625d6</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Data Architect</t>
+          <t>Senior Data Engineer - Cloud Data Platform</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>YETI</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Vertex AI, Scala, Databricks Lakehouse</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Informatica PowerCenter, Data Modeling, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c9a108f2d63b6a3</t>
+          <t>https://www.indeed.com/viewjob?jk=de80a4e1ea3c7456</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Architect – Manufacturing Test</t>
+          <t>Senior Forward Deployed Engineer - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cerebras Systems</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c04a9f371533f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=99421b7cddeacb9e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Engineer, Software Automation Test Architect</t>
+          <t>Data Scientist Associate – Product, Experience and Technology (PXT) Analytics Team</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Spectra Logic</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b0e0a0263f945e7</t>
+          <t>https://www.indeed.com/viewjob?jk=e733ae2cd5148257</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Architect – Manufacturing Test</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cerebras Systems</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ec3a8e9018054</t>
+          <t>https://www.indeed.com/viewjob?jk=e71383b94e86fbaa</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2941,29 +2941,29 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca392fa39b84631e</t>
+          <t>https://www.indeed.com/viewjob?jk=c5acf07a00ef614c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, App</t>
+          <t>Sr. Data Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>YETI</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Vertex AI, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f024bf694f893ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=6c9a108f2d63b6a3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Scientist Associate – Product, Experience and Technology (PXT) Analytics Team</t>
+          <t>MuleSoft/Python Software Engineer - OIT</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Emory University</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+          <t>AWS, S3, IAM, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e733ae2cd5148257</t>
+          <t>https://www.indeed.com/viewjob?jk=a511e772aaa75c08</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Software Architect – Manufacturing Test</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Cerebras Systems</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e71383b94e86fbaa</t>
+          <t>https://www.indeed.com/viewjob?jk=1c04a9f371533f2c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Security Engineer - Vuln Management (Infra)</t>
+          <t>Engineer, Software Automation Test Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Replit</t>
+          <t>Spectra Logic</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f8e63a431463bc</t>
+          <t>https://www.indeed.com/viewjob?jk=9b0e0a0263f945e7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Software Architect – Manufacturing Test</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Cerebras Systems</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed909357965ec568</t>
+          <t>https://www.indeed.com/viewjob?jk=132ec3a8e9018054</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Senior Software Engineer, App</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a49347bb46652a75</t>
+          <t>https://www.indeed.com/viewjob?jk=ca392fa39b84631e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer, App</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cf30157db81ea0e</t>
+          <t>https://www.indeed.com/viewjob?jk=f024bf694f893ebe</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>API Gateway, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b8a567bdd35f252</t>
+          <t>https://www.indeed.com/viewjob?jk=a8dc47a59b46765c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Instuctor , Cloud Computing &amp; Devops(CCDO)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Fullstack Academy</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e70cddc4d406c6fc</t>
+          <t>https://www.indeed.com/viewjob?jk=81ff13fcbdc21173</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nexstar Media Group, Inc.</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b532541851ceb06</t>
+          <t>https://www.indeed.com/viewjob?jk=ed909357965ec568</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,17 +3321,227 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a49347bb46652a75</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cf30157db81ea0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b8a567bdd35f252</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e70cddc4d406c6fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Nexstar Media Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b532541851ceb06</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Recutify Inc.</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>AWS, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes, CloudWatch</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2ee880f838d01800</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Security Engineer - Vuln Management (Infra)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Replit</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06f8e63a431463bc</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-27.xlsx
+++ b/results/job_matches_2026-05-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,20 +473,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Klaxon Technolgies</t>
+          <t>A-TEK Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>39.6</v>
+        <v>25.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, RDS</t>
+          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,102 +496,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3265598d80fd8a76</t>
+          <t>https://www.indeed.com/viewjob?jk=fdcddba2d97d56f1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Forward Deployed Engineer - Data Migration &amp; Data Consolidation Platforms</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A-TEK Inc</t>
+          <t>Rackspace Technology</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25.7</v>
+        <v>25</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle</t>
+          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdcddba2d97d56f1</t>
+          <t>https://www.indeed.com/viewjob?jk=b3063b040bfb390f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - Data Migration &amp; Data Consolidation Platforms</t>
+          <t>Java Springwood Backend Developer (Hybrid)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rackspace Technology</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>23.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, Azure</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3063b040bfb390f</t>
+          <t>https://www.indeed.com/viewjob?jk=12483420b6facc39</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Java Springwood Backend Developer (Hybrid)</t>
+          <t>Senior Analytics Engineer, People Data</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, Azure</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12483420b6facc39</t>
+          <t>https://www.indeed.com/viewjob?jk=d5886aefde3a2ed5</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,94 +636,94 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5886aefde3a2ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=392458a76ed6493b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, People Data</t>
+          <t>Specialist Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>22.9</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, BigQuery, Spark</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=392458a76ed6493b</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff097337c23c8bf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Platform Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Leadfeeder</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM, RDS, Databricks</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Hadoop, HDFS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2b659aa81b3c306</t>
+          <t>https://www.indeed.com/viewjob?jk=87f70fa8d4be0571</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,52 +731,52 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Hadoop, HDFS, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87f70fa8d4be0571</t>
+          <t>https://www.indeed.com/viewjob?jk=366df588234a7c92</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Lakehouse Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SEACORP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Manassas, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Glue, S3, RDS, Hadoop, Hive, Spark, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366df588234a7c92</t>
+          <t>https://www.indeed.com/viewjob?jk=790599fa002d6633</t>
         </is>
       </c>
     </row>
@@ -841,29 +841,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=196506204c7c944f</t>
+          <t>https://www.indeed.com/viewjob?jk=e2976c8aa5f80420</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full Stack Agentic AI Developer</t>
+          <t>Software Engineer, I - Data Engineering</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6782ecd37a1a284</t>
+          <t>https://www.indeed.com/viewjob?jk=196506204c7c944f</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=770d98b3f2c61a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=2322ef59d1218d09</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b965cc65d75bb68</t>
+          <t>https://www.indeed.com/viewjob?jk=770d98b3f2c61a3f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Architect/Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rockwell Automation</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Polars, PostgreSQL, Azure Cosmos DB, NoSQL, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc83cb585d053a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=4b965cc65d75bb68</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer III, Voice AI</t>
+          <t>Senior Agentic AI Architect/Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Natera</t>
+          <t>Rockwell Automation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Azure, Scala, Kafka</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Polars, PostgreSQL, Azure Cosmos DB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff57ba86e213734</t>
+          <t>https://www.indeed.com/viewjob?jk=cc83cb585d053a0f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Modem Machine Learning Engineer</t>
+          <t>Software Engineer III, Voice AI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Natera</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Azure, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3f6235da80ec1d</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff57ba86e213734</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>Modem Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=960f767365c3fdc0</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3f6235da80ec1d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pr AI Cloud Systems Engineer (RITM0479748)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Discount Tire</t>
+          <t>Grand Circle Travel</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc9dfce7125ed878</t>
+          <t>https://www.indeed.com/viewjob?jk=54baeed1bb9bcd57</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Pr AI Cloud Systems Engineer (RITM0479748)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Discount Tire</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,29 +1151,29 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd51c65d58c91761</t>
+          <t>https://www.indeed.com/viewjob?jk=dc9dfce7125ed878</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Quarterhill</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c6d1fd76fe3448</t>
+          <t>https://www.indeed.com/viewjob?jk=87ab23efc926ec48</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bessemer Trust</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=774b596dfb394ced</t>
+          <t>https://www.indeed.com/viewjob?jk=b01264aaa08f1855</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Bessemer Trust</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e2e8c07008edb9</t>
+          <t>https://www.indeed.com/viewjob?jk=774b596dfb394ced</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Quarterhill</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ab23efc926ec48</t>
+          <t>https://www.indeed.com/viewjob?jk=fd51c65d58c91761</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01264aaa08f1855</t>
+          <t>https://www.indeed.com/viewjob?jk=66c6d1fd76fe3448</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026012 - Senior Software Analyst</t>
+          <t>Full Stack Developer / Cloud Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>Keystone Sports Construction</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenixville, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Azure, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59907092ed75df82</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a62b9aa861f18b</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Allruva Technology Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, HDFS, Hive, MapReduce, HBase, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3fc6d4b0669cc2e</t>
+          <t>https://www.indeed.com/viewjob?jk=e62a0487a6b58cf5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Data Engineer (Azure &amp; Databricks)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62a0487a6b58cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=634ea8c9beab0812</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure &amp; Databricks)</t>
+          <t>AWS Data Engineer (Cloud Data Platform &amp; Pipeline Specialist) (FTE / Onsite)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=634ea8c9beab0812</t>
+          <t>https://www.indeed.com/viewjob?jk=2feefef0c932976c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AWS Data Engineer (Cloud Data Platform &amp; Pipeline Specialist) (FTE / Onsite)</t>
+          <t>Senior Data Engineer (Azure &amp; Databricks)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2feefef0c932976c</t>
+          <t>https://www.indeed.com/viewjob?jk=dd215d5414c53bc0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure &amp; Databricks)</t>
+          <t>Senior Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Specialty Building Products</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd215d5414c53bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=6435e356286a621f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Full Stack Application Developer</t>
+          <t>Architecture Senior Advisor</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Specialty Building Products</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, ECS, RDS, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6435e356286a621f</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd686e8a6d93c00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer - Catalogs, Hierarchy &amp; OrgMDM (Hybrid - Seattle, WA)</t>
+          <t>Architecture Senior Advisor</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Kafka, PostgreSQL, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, ECS, RDS, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f82aaa0bacb5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=a100c3ae58674b37</t>
         </is>
       </c>
     </row>
@@ -1728,60 +1728,60 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Emerging Technologies (AI, GenAI, ML)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Empower</t>
+          <t>Holtzbrinck Publishing Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Vertex AI, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21e1b2180a79f7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=6553fe8d88b5cc2c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Architecture Senior Advisor</t>
+          <t>Data Engineer II - Surgery</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd686e8a6d93c00</t>
+          <t>https://www.indeed.com/viewjob?jk=443f2bd8cdbdcd91</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Architecture Senior Advisor</t>
+          <t>Senior Engineer 2: AI Agentic Solutions (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,19 +1826,19 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a100c3ae58674b37</t>
+          <t>https://www.indeed.com/viewjob?jk=d1942d9ec58e935c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Prime Cargo People Logistics</t>
+          <t>Macmillan Publishers</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1847,11 +1847,11 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, GCP, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c504b34cabd6342d</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb1d2668d2c3bb3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Holtzbrinck Publishing Group</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6553fe8d88b5cc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=06c0ec6191f51dd9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer II - Surgery</t>
+          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443f2bd8cdbdcd91</t>
+          <t>https://www.indeed.com/viewjob?jk=4a46908cd0a69c52</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Engineer 2: AI Agentic Solutions (Hybrid - Seattle, WA)</t>
+          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1942d9ec58e935c</t>
+          <t>https://www.indeed.com/viewjob?jk=2d887191c1e6747a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Macmillan Publishers</t>
+          <t>Specialized Dental</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Data Factory, Medallion Architecture, Scala, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb1d2668d2c3bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=97619fb277569f5d</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Software Engineer- Forward Deployed</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Butler Till</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50977d506f8a126</t>
+          <t>https://www.indeed.com/viewjob?jk=bda2c2b8bdd5703d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Kafka Developer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Butler Till</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd25b4ca05cd6b8c</t>
+          <t>https://www.indeed.com/viewjob?jk=b50977d506f8a126</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,42 +2316,42 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8cd3096eac30881</t>
+          <t>https://www.indeed.com/viewjob?jk=78902f746ba9d9e9</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78902f746ba9d9e9</t>
+          <t>https://www.indeed.com/viewjob?jk=8ceb9d089a51d56c</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Engineer II, AWS Connect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
+          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3acabec1c779e4f7</t>
+          <t>https://www.indeed.com/viewjob?jk=8383bcaf3f0d64cd</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Acquire-Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BehaviorSpan</t>
+          <t>BRUNT Workwear</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a716d21991893978</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a66e52ac0ae1b3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Always Compassionate Health</t>
+          <t>BRUNT Workwear</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>North Reading, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e602a7ae37682d44</t>
+          <t>https://www.indeed.com/viewjob?jk=ed9ff440388b3f76</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Snowflake Engineer</t>
+          <t>Engineer II, AWS Connect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=002369ff092a4302</t>
+          <t>https://www.indeed.com/viewjob?jk=3acabec1c779e4f7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Acquire-Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>BehaviorSpan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6ec5c4dd06dea5</t>
+          <t>https://www.indeed.com/viewjob?jk=a716d21991893978</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>Always Compassionate Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623ad57a66a94f1a</t>
+          <t>https://www.indeed.com/viewjob?jk=e602a7ae37682d44</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Interra Health</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dffdb4bf979c0c04</t>
+          <t>https://www.indeed.com/viewjob?jk=f31a5af9350429b9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer II - Java/Python</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,112 +2656,112 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e901ac4878117ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=5a1dc59f217f9fce</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
+          <t>Azure Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Newsbreak</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f967de110027227c</t>
+          <t>https://www.indeed.com/viewjob?jk=df60f817f0201540</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
+          <t>Platform Engineering Architect - AI Automation</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Newsbreak</t>
+          <t>Clarity Innovations, LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Jessup, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea855ad903dd71df</t>
+          <t>https://www.indeed.com/viewjob?jk=2d32c274c61b107e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877d45e3d1a625d6</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6ec5c4dd06dea5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Cloud Data Platform</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Enlyte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Informatica PowerCenter, Data Modeling, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de80a4e1ea3c7456</t>
+          <t>https://www.indeed.com/viewjob?jk=623ad57a66a94f1a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed Engineer - QuantumBlack, AI by McKinsey</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Interra Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,59 +2841,59 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99421b7cddeacb9e</t>
+          <t>https://www.indeed.com/viewjob?jk=dffdb4bf979c0c04</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Scientist Associate – Product, Experience and Technology (PXT) Analytics Team</t>
+          <t>Software Engineer II - Java/Python</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e733ae2cd5148257</t>
+          <t>https://www.indeed.com/viewjob?jk=e901ac4878117ce6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Newsbreak</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e71383b94e86fbaa</t>
+          <t>https://www.indeed.com/viewjob?jk=f967de110027227c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, App</t>
+          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Newsbreak</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5acf07a00ef614c</t>
+          <t>https://www.indeed.com/viewjob?jk=ea855ad903dd71df</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>YETI</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Vertex AI, Scala, Databricks Lakehouse</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c9a108f2d63b6a3</t>
+          <t>https://www.indeed.com/viewjob?jk=877d45e3d1a625d6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MuleSoft/Python Software Engineer - OIT</t>
+          <t>Senior Data Engineer - Cloud Data Platform</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Emory University</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Informatica PowerCenter, Data Modeling, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a511e772aaa75c08</t>
+          <t>https://www.indeed.com/viewjob?jk=de80a4e1ea3c7456</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Architect – Manufacturing Test</t>
+          <t>Senior Forward Deployed Engineer - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cerebras Systems</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c04a9f371533f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=99421b7cddeacb9e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Engineer, Software Automation Test Architect</t>
+          <t>Senior Software Engineer, App</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Spectra Logic</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b0e0a0263f945e7</t>
+          <t>https://www.indeed.com/viewjob?jk=c5acf07a00ef614c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Architect – Manufacturing Test</t>
+          <t>MuleSoft/Python Software Engineer - OIT</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cerebras Systems</t>
+          <t>Emory University</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, S3, IAM, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ec3a8e9018054</t>
+          <t>https://www.indeed.com/viewjob?jk=a511e772aaa75c08</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, App</t>
+          <t>Sr. Data Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>YETI</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Vertex AI, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca392fa39b84631e</t>
+          <t>https://www.indeed.com/viewjob?jk=6c9a108f2d63b6a3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, App</t>
+          <t>Software Architect – Manufacturing Test</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Cerebras Systems</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f024bf694f893ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=1c04a9f371533f2c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Engineer, Software Automation Test Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Spectra Logic</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8dc47a59b46765c</t>
+          <t>https://www.indeed.com/viewjob?jk=9b0e0a0263f945e7</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Instuctor , Cloud Computing &amp; Devops(CCDO)</t>
+          <t>Software Architect – Manufacturing Test</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Fullstack Academy</t>
+          <t>Cerebras Systems</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ff13fcbdc21173</t>
+          <t>https://www.indeed.com/viewjob?jk=132ec3a8e9018054</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>API Gateway, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed909357965ec568</t>
+          <t>https://www.indeed.com/viewjob?jk=a8dc47a59b46765c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Data Scientist Associate – Product, Experience and Technology (PXT) Analytics Team</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a49347bb46652a75</t>
+          <t>https://www.indeed.com/viewjob?jk=e733ae2cd5148257</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cf30157db81ea0e</t>
+          <t>https://www.indeed.com/viewjob?jk=e71383b94e86fbaa</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer, App</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b8a567bdd35f252</t>
+          <t>https://www.indeed.com/viewjob?jk=ca392fa39b84631e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Software Engineer, App</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e70cddc4d406c6fc</t>
+          <t>https://www.indeed.com/viewjob?jk=f024bf694f893ebe</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Nexstar Media Group, Inc.</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b532541851ceb06</t>
+          <t>https://www.indeed.com/viewjob?jk=ed909357965ec568</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes, CloudWatch</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ee880f838d01800</t>
+          <t>https://www.indeed.com/viewjob?jk=a49347bb46652a75</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Security Engineer - Vuln Management (Infra)</t>
+          <t>Instuctor , Cloud Computing &amp; Devops(CCDO)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Replit</t>
+          <t>Fullstack Academy</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,17 +3531,157 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f8e63a431463bc</t>
+          <t>https://www.indeed.com/viewjob?jk=81ff13fcbdc21173</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cf30157db81ea0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b8a567bdd35f252</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e70cddc4d406c6fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Nexstar Media Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b532541851ceb06</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-27.xlsx
+++ b/results/job_matches_2026-05-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (AWS Glue, Airflow, Lambda, Postgres)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Hadoop, HDFS, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, S3, SNS, IAM, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87f70fa8d4be0571</t>
+          <t>https://www.indeed.com/viewjob?jk=acfc187789a37a56</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer (AWS Glue, Airflow, Lambda, Postgres)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Glue, Lambda, S3, SNS, IAM, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366df588234a7c92</t>
+          <t>https://www.indeed.com/viewjob?jk=0579b411528126ab</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Lakehouse Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SEACORP</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Manassas, VA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Hadoop, Hive, Spark, Scala, Kafka, MongoDB</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Hadoop, HDFS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=790599fa002d6633</t>
+          <t>https://www.indeed.com/viewjob?jk=87f70fa8d4be0571</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Developer / AWS Solutions Architect with .Net integration</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cloud data Systems US</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Oracle, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e523bf5a5bf5d62b</t>
+          <t>https://www.indeed.com/viewjob?jk=be4853042949bdd1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer, I - Data Engineering</t>
+          <t>Senior DevOps Engineer – Data Engineering</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TORC Robotics</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2976c8aa5f80420</t>
+          <t>https://www.indeed.com/viewjob?jk=7f642c610470a071</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer, I - Data Engineering</t>
+          <t>DevOps Engineer – Data Engineering</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TORC Robotics</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=196506204c7c944f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c81fd4cfc405e48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Data Engineer (in person)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>SEP</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Westfield, IN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,19 +916,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2322ef59d1218d09</t>
+          <t>https://www.indeed.com/viewjob?jk=586f1008eb3dc860</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -941,24 +941,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=770d98b3f2c61a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=e523bf5a5bf5d62b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,155 +968,155 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b965cc65d75bb68</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ef9537310f7214</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Architect/Engineer</t>
+          <t>Software Engineer, I - Data Engineering</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rockwell Automation</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Polars, PostgreSQL, Azure Cosmos DB, NoSQL, MLOps</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc83cb585d053a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=e2976c8aa5f80420</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer III, Voice AI</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Natera</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Azure, Scala, Kafka</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff57ba86e213734</t>
+          <t>https://www.indeed.com/viewjob?jk=2322ef59d1218d09</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Modem Machine Learning Engineer</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3f6235da80ec1d</t>
+          <t>https://www.indeed.com/viewjob?jk=770d98b3f2c61a3f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI Data Specialist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Grand Circle Travel</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Spark, PySpark, Scala, PostgreSQL, DataOps, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54baeed1bb9bcd57</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ddb8e746b2d111</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pr AI Cloud Systems Engineer (RITM0479748)</t>
+          <t>Java ReactJS AWS Developer Payments</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Discount Tire</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,137 +1161,137 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc9dfce7125ed878</t>
+          <t>https://www.indeed.com/viewjob?jk=213ccd9512c0c9dc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Quarterhill</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ab23efc926ec48</t>
+          <t>https://www.indeed.com/viewjob?jk=424703caefd6d113</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01264aaa08f1855</t>
+          <t>https://www.indeed.com/viewjob?jk=101061bea2a8593b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Modem Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bessemer Trust</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=774b596dfb394ced</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3f6235da80ec1d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III, Voice AI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Natera</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Azure, Scala, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd51c65d58c91761</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff57ba86e213734</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c6d1fd76fe3448</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd094809bea2029</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Developer / Cloud Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Keystone Sports Construction</t>
+          <t>Grand Circle Travel</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phoenixville, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Azure, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a62b9aa861f18b</t>
+          <t>https://www.indeed.com/viewjob?jk=54baeed1bb9bcd57</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Pr AI Cloud Systems Engineer (RITM0479748)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Quarterhill</t>
+          <t>Discount Tire</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,147 +1396,147 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b056aa8ae1df1b</t>
+          <t>https://www.indeed.com/viewjob?jk=dc9dfce7125ed878</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Bessemer Trust</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0a72f863d410844</t>
+          <t>https://www.indeed.com/viewjob?jk=774b596dfb394ced</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62a0487a6b58cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=fd51c65d58c91761</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure &amp; Databricks)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=634ea8c9beab0812</t>
+          <t>https://www.indeed.com/viewjob?jk=66c6d1fd76fe3448</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AWS Data Engineer (Cloud Data Platform &amp; Pipeline Specialist) (FTE / Onsite)</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,94 +1546,94 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2feefef0c932976c</t>
+          <t>https://www.indeed.com/viewjob?jk=b01264aaa08f1855</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure &amp; Databricks)</t>
+          <t>Full Stack Developer / Cloud Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Keystone Sports Construction</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenixville, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Azure, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd215d5414c53bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a62b9aa861f18b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Full Stack Application Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Specialty Building Products</t>
+          <t>Quarterhill</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6435e356286a621f</t>
+          <t>https://www.indeed.com/viewjob?jk=87ab23efc926ec48</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Architecture Senior Advisor</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd686e8a6d93c00</t>
+          <t>https://www.indeed.com/viewjob?jk=a0a72f863d410844</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Architecture Senior Advisor</t>
+          <t>Data Engineer (Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Time Travel, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a100c3ae58674b37</t>
+          <t>https://www.indeed.com/viewjob?jk=3e3f82c93d576f7a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,182 +1711,182 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1985124aab93f8b5</t>
+          <t>https://www.indeed.com/viewjob?jk=e62a0487a6b58cf5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AWS Data Engineer (Cloud Data Platform &amp; Pipeline Specialist) (FTE / Onsite)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Holtzbrinck Publishing Group</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6553fe8d88b5cc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=2feefef0c932976c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer II - Surgery</t>
+          <t>Senior Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Specialty Building Products</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443f2bd8cdbdcd91</t>
+          <t>https://www.indeed.com/viewjob?jk=6435e356286a621f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Engineer 2: AI Agentic Solutions (Hybrid - Seattle, WA)</t>
+          <t>Consulting Associate/Full Stack Developer (Forensic Services practice)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Charles River Associates</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Scala, DynamoDB, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1942d9ec58e935c</t>
+          <t>https://www.indeed.com/viewjob?jk=811330ccc62c3998</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Consulting Associate/Full Stack Developer (Forensic Services practice)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Macmillan Publishers</t>
+          <t>Charles River Associates</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Scala, DynamoDB, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb1d2668d2c3bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=6c0c76defeb29f13</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
+          <t>Consulting Associate/Full Stack Developer (Forensic Services practice)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Charles River Associates</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Scala, DynamoDB, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c0ec6191f51dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=3abca339dffff6de</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
+          <t>Consulting Associate/Full Stack Developer (Forensic Services practice)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Charles River Associates</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Scala, DynamoDB, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a46908cd0a69c52</t>
+          <t>https://www.indeed.com/viewjob?jk=990baac9a4b4d3c5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
+          <t>Consulting Associate/Full Stack Developer (Forensic Services practice)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Charles River Associates</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Scala, DynamoDB, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d887191c1e6747a</t>
+          <t>https://www.indeed.com/viewjob?jk=853dfe0e00183c55</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Architecture Senior Advisor</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Specialized Dental</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Medallion Architecture, Scala, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, Redshift, ECS, RDS, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97619fb277569f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd686e8a6d93c00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack AI + Data Engineer</t>
+          <t>Architecture Senior Advisor</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Techtorch</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Spark Streaming, Kafka, PostgreSQL, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, ECS, RDS, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6740052e5af1c2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=a100c3ae58674b37</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026011 - Operations Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>Holtzbrinck Publishing Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21cc17fa6fcb98f8</t>
+          <t>https://www.indeed.com/viewjob?jk=6553fe8d88b5cc2c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior AWS Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4df4e36af097a7</t>
+          <t>https://www.indeed.com/viewjob?jk=403a9d53356963ed</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>Data Engineer II - Surgery</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2be82c2c579e7f0</t>
+          <t>https://www.indeed.com/viewjob?jk=443f2bd8cdbdcd91</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Dask, NoSQL, MLOps, MLflow, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3462d2e2223e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=c9cf0398eaa58c55</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kinsale Management Inc</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a938739108dd1870</t>
+          <t>https://www.indeed.com/viewjob?jk=16d25674f9943018</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Forward Deployed</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda2c2b8bdd5703d</t>
+          <t>https://www.indeed.com/viewjob?jk=709d2dc8e12638c5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Butler Till</t>
+          <t>Lyra Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Tableau, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50977d506f8a126</t>
+          <t>https://www.indeed.com/viewjob?jk=c13b3570f31644de</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,42 +2306,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78902f746ba9d9e9</t>
+          <t>https://www.indeed.com/viewjob?jk=760e0caf358fa7ba</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ceb9d089a51d56c</t>
+          <t>https://www.indeed.com/viewjob?jk=06c0ec6191f51dd9</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6f76b9337a13b3</t>
+          <t>https://www.indeed.com/viewjob?jk=4a46908cd0a69c52</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8383bcaf3f0d64cd</t>
+          <t>https://www.indeed.com/viewjob?jk=2d887191c1e6747a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack AI + Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BRUNT Workwear</t>
+          <t>Techtorch</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
+          <t>AWS, Azure, Spark, Spark Streaming, Kafka, PostgreSQL, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a66e52ac0ae1b3</t>
+          <t>https://www.indeed.com/viewjob?jk=6740052e5af1c2fe</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BRUNT Workwear</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>North Reading, MA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,137 +2491,137 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed9ff440388b3f76</t>
+          <t>https://www.indeed.com/viewjob?jk=24a63124749b1283</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Engineer II, AWS Connect</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3acabec1c779e4f7</t>
+          <t>https://www.indeed.com/viewjob?jk=9ef589b39c6904ab</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Acquire-Site Reliability Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BehaviorSpan</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a716d21991893978</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae687a47012d375</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Always Compassionate Health</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e602a7ae37682d44</t>
+          <t>https://www.indeed.com/viewjob?jk=526789b5a039d9e4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31a5af9350429b9</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab868ce436a523f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Constitution Surgery Alliance</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,137 +2666,137 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a1dc59f217f9fce</t>
+          <t>https://www.indeed.com/viewjob?jk=8e91aba2a71eea06</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Azure Data Warehouse Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df60f817f0201540</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4df4e36af097a7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Platform Engineering Architect - AI Automation</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Clarity Innovations, LLC</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jessup, MD, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d32c274c61b107e</t>
+          <t>https://www.indeed.com/viewjob?jk=c2be82c2c579e7f0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer- Forward Deployed</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6ec5c4dd06dea5</t>
+          <t>https://www.indeed.com/viewjob?jk=bda2c2b8bdd5703d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>Kinsale Management Inc</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623ad57a66a94f1a</t>
+          <t>https://www.indeed.com/viewjob?jk=a938739108dd1870</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Interra Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dffdb4bf979c0c04</t>
+          <t>https://www.indeed.com/viewjob?jk=78902f746ba9d9e9</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer II - Java/Python</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Radar</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,134 +2866,134 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Vertex AI, Spark, Scala, Kafka, Dask, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e901ac4878117ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=f34740da82b33461</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Newsbreak</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f967de110027227c</t>
+          <t>https://www.indeed.com/viewjob?jk=8ceb9d089a51d56c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Newsbreak</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea855ad903dd71df</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6f76b9337a13b3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Platform Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877d45e3d1a625d6</t>
+          <t>https://www.indeed.com/viewjob?jk=16a9b21087d9070b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Cloud Data Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3002,81 +3002,81 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Informatica PowerCenter, Data Modeling, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de80a4e1ea3c7456</t>
+          <t>https://www.indeed.com/viewjob?jk=8383bcaf3f0d64cd</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed Engineer - QuantumBlack, AI by McKinsey</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>BRUNT Workwear</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99421b7cddeacb9e</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a66e52ac0ae1b3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, App</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>BRUNT Workwear</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>North Reading, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5acf07a00ef614c</t>
+          <t>https://www.indeed.com/viewjob?jk=ed9ff440388b3f76</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MuleSoft/Python Software Engineer - OIT</t>
+          <t>Engineer II, AWS Connect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Emory University</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a511e772aaa75c08</t>
+          <t>https://www.indeed.com/viewjob?jk=3acabec1c779e4f7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Data Architect</t>
+          <t>Acquire-Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>YETI</t>
+          <t>BehaviorSpan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Vertex AI, Scala, Databricks Lakehouse</t>
+          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,172 +3156,172 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c9a108f2d63b6a3</t>
+          <t>https://www.indeed.com/viewjob?jk=a716d21991893978</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Architect – Manufacturing Test</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cerebras Systems</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c04a9f371533f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=010c395bdcd7a30d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Engineer, Software Automation Test Architect</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Spectra Logic</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b0e0a0263f945e7</t>
+          <t>https://www.indeed.com/viewjob?jk=f31a5af9350429b9</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Architect – Manufacturing Test</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cerebras Systems</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ec3a8e9018054</t>
+          <t>https://www.indeed.com/viewjob?jk=5a1dc59f217f9fce</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Azure Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8dc47a59b46765c</t>
+          <t>https://www.indeed.com/viewjob?jk=df60f817f0201540</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Scientist Associate – Product, Experience and Technology (PXT) Analytics Team</t>
+          <t>Platform Engineering Architect - AI Automation</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Clarity Innovations, LLC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jessup, MD, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,102 +3331,102 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e733ae2cd5148257</t>
+          <t>https://www.indeed.com/viewjob?jk=2d32c274c61b107e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e71383b94e86fbaa</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6ec5c4dd06dea5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, App</t>
+          <t>Senior IT Analyst Applications</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca392fa39b84631e</t>
+          <t>https://www.indeed.com/viewjob?jk=16716305f57ba769</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, App</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Enlyte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f024bf694f893ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=623ad57a66a94f1a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Interra Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed909357965ec568</t>
+          <t>https://www.indeed.com/viewjob?jk=dffdb4bf979c0c04</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Newsbreak</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a49347bb46652a75</t>
+          <t>https://www.indeed.com/viewjob?jk=f967de110027227c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Instuctor , Cloud Computing &amp; Devops(CCDO)</t>
+          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Fullstack Academy</t>
+          <t>Newsbreak</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ff13fcbdc21173</t>
+          <t>https://www.indeed.com/viewjob?jk=ea855ad903dd71df</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Jenkins, Git</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cf30157db81ea0e</t>
+          <t>https://www.indeed.com/viewjob?jk=877d45e3d1a625d6</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer - Cloud Data Platform</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Informatica PowerCenter, Data Modeling, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b8a567bdd35f252</t>
+          <t>https://www.indeed.com/viewjob?jk=de80a4e1ea3c7456</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e70cddc4d406c6fc</t>
+          <t>https://www.indeed.com/viewjob?jk=3fc83920e558138a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Software Engineer, App</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Nexstar Media Group, Inc.</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,17 +3671,542 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5acf07a00ef614c</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>MuleSoft/Python Software Engineer - OIT</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Emory University</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a511e772aaa75c08</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>API Gateway, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8dc47a59b46765c</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Business Informatics Support Data Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Trillium Health Resources</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed909357965ec568</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Business Informatics Support Data Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Trillium Health Resources</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a49347bb46652a75</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Instuctor , Cloud Computing &amp; Devops(CCDO)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Fullstack Academy</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81ff13fcbdc21173</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Software Architect – Manufacturing Test</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Cerebras Systems</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c04a9f371533f2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Software Architect – Manufacturing Test</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Cerebras Systems</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=132ec3a8e9018054</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Data Scientist Associate – Product, Experience and Technology (PXT) Analytics Team</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e733ae2cd5148257</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Sr. Data Architect</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>YETI</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Vertex AI, Scala, Databricks Lakehouse</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c9a108f2d63b6a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Nexstar Media Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
           <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7b532541851ceb06</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b8a567bdd35f252</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cf30157db81ea0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e70cddc4d406c6fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Junior AI Platform Engineer, Infrastrucure</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>accrete</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5496a0bc2b4bd3eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Lila Sciences</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e71383b94e86fbaa</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-27.xlsx
+++ b/results/job_matches_2026-05-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Java Springwood Backend Developer (Hybrid)</t>
+          <t>Senior Analytics Engineer, People Data</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, Azure</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12483420b6facc39</t>
+          <t>https://www.indeed.com/viewjob?jk=d5886aefde3a2ed5</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5886aefde3a2ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=392458a76ed6493b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, People Data</t>
+          <t>Enterprise Data Warehouse (EDW) ETL/Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>22.9</v>
+        <v>20.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, BigQuery, Spark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=392458a76ed6493b</t>
+          <t>https://www.indeed.com/viewjob?jk=2655650a85cb9fcd</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Specialist Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff097337c23c8bf</t>
+          <t>https://www.indeed.com/viewjob?jk=e069ef7a7b20f315</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS Glue, Airflow, Lambda, Postgres)</t>
+          <t>Specialist Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, IAM, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acfc187789a37a56</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff097337c23c8bf</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0579b411528126ab</t>
+          <t>https://www.indeed.com/viewjob?jk=acfc187789a37a56</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (AWS Glue, Airflow, Lambda, Postgres)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Hadoop, HDFS, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, S3, SNS, IAM, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87f70fa8d4be0571</t>
+          <t>https://www.indeed.com/viewjob?jk=0579b411528126ab</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Developer / AWS Solutions Architect with .Net integration</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cloud data Systems US</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Oracle, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Hadoop, HDFS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be4853042949bdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=87f70fa8d4be0571</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer – Data Engineering</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f642c610470a071</t>
+          <t>https://www.indeed.com/viewjob?jk=95c2b1e94f1ace71</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Engineer – Data Engineering</t>
+          <t>Cloud Developer / AWS Solutions Architect with .Net integration</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Cloud data Systems US</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Oracle, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c81fd4cfc405e48</t>
+          <t>https://www.indeed.com/viewjob?jk=be4853042949bdd1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer (in person)</t>
+          <t>DevOps Engineer – Data Engineering</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SEP</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Westfield, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586f1008eb3dc860</t>
+          <t>https://www.indeed.com/viewjob?jk=5c81fd4cfc405e48</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer – Data Engineering</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e523bf5a5bf5d62b</t>
+          <t>https://www.indeed.com/viewjob?jk=7f642c610470a071</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Engineering</t>
+          <t>Data Engineer (in person)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SEP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Westfield, IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ef9537310f7214</t>
+          <t>https://www.indeed.com/viewjob?jk=586f1008eb3dc860</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer, I - Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TORC Robotics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2976c8aa5f80420</t>
+          <t>https://www.indeed.com/viewjob?jk=e523bf5a5bf5d62b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Senior Software Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2322ef59d1218d09</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ef9537310f7214</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Software Engineer, I - Data Engineering</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=770d98b3f2c61a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=e2976c8aa5f80420</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Data Specialist</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Spark, PySpark, Scala, PostgreSQL, DataOps, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ddb8e746b2d111</t>
+          <t>https://www.indeed.com/viewjob?jk=2322ef59d1218d09</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Java ReactJS AWS Developer Payments</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=213ccd9512c0c9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=770d98b3f2c61a3f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Data Specialist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>RDS, Spark, PySpark, Scala, PostgreSQL, DataOps, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424703caefd6d113</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ddb8e746b2d111</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101061bea2a8593b</t>
+          <t>https://www.indeed.com/viewjob?jk=2002a3bb054db4fd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Modem Machine Learning Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3f6235da80ec1d</t>
+          <t>https://www.indeed.com/viewjob?jk=dae15109dd782046</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer III, Voice AI</t>
+          <t>Java ReactJS AWS Developer Payments</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Natera</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,42 +1291,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Azure, Scala, Kafka</t>
+          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff57ba86e213734</t>
+          <t>https://www.indeed.com/viewjob?jk=213ccd9512c0c9dc</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd094809bea2029</t>
+          <t>https://www.indeed.com/viewjob?jk=424703caefd6d113</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Grand Circle Travel</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54baeed1bb9bcd57</t>
+          <t>https://www.indeed.com/viewjob?jk=101061bea2a8593b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Pr AI Cloud Systems Engineer (RITM0479748)</t>
+          <t>Modem Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Discount Tire</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc9dfce7125ed878</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3f6235da80ec1d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bessemer Trust</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=774b596dfb394ced</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd094809bea2029</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Grand Circle Travel</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd51c65d58c91761</t>
+          <t>https://www.indeed.com/viewjob?jk=54baeed1bb9bcd57</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Pr AI Cloud Systems Engineer (RITM0479748)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Discount Tire</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c6d1fd76fe3448</t>
+          <t>https://www.indeed.com/viewjob?jk=dc9dfce7125ed878</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Full Stack Developer / Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Keystone Sports Construction</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Phoenixville, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Azure, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01264aaa08f1855</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a62b9aa861f18b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full Stack Developer / Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Keystone Sports Construction</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phoenixville, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,29 +1571,29 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Azure, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a62b9aa861f18b</t>
+          <t>https://www.indeed.com/viewjob?jk=fd51c65d58c91761</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Quarterhill</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ab23efc926ec48</t>
+          <t>https://www.indeed.com/viewjob?jk=66c6d1fd76fe3448</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>DNS Solutions Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,59 +1651,59 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0a72f863d410844</t>
+          <t>https://www.indeed.com/viewjob?jk=c46f3131e66c1a54</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake, AWS)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Quarterhill</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Time Travel, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e3f82c93d576f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=87ab23efc926ec48</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62a0487a6b58cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=a0a72f863d410844</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AWS Data Engineer (Cloud Data Platform &amp; Pipeline Specialist) (FTE / Onsite)</t>
+          <t>Data Engineer (Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Time Travel, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2feefef0c932976c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e3f82c93d576f7a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Full Stack Application Developer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Specialty Building Products</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6435e356286a621f</t>
+          <t>https://www.indeed.com/viewjob?jk=e62a0487a6b58cf5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Consulting Associate/Full Stack Developer (Forensic Services practice)</t>
+          <t>AWS Data Engineer (Cloud Data Platform &amp; Pipeline Specialist) (FTE / Onsite)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Charles River Associates</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Scala, DynamoDB, Docker</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=811330ccc62c3998</t>
+          <t>https://www.indeed.com/viewjob?jk=2feefef0c932976c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Consulting Associate/Full Stack Developer (Forensic Services practice)</t>
+          <t>Senior Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Charles River Associates</t>
+          <t>Specialty Building Products</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Scala, DynamoDB, Docker</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c0c76defeb29f13</t>
+          <t>https://www.indeed.com/viewjob?jk=6435e356286a621f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Consulting Associate/Full Stack Developer (Forensic Services practice)</t>
+          <t>Architecture Senior Advisor</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Charles River Associates</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,42 +1886,42 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Scala, DynamoDB, Docker</t>
+          <t>AWS, Redshift, ECS, RDS, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abca339dffff6de</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd686e8a6d93c00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Consulting Associate/Full Stack Developer (Forensic Services practice)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Charles River Associates</t>
+          <t>Holtzbrinck Publishing Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Scala, DynamoDB, Docker</t>
+          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,129 +1931,129 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990baac9a4b4d3c5</t>
+          <t>https://www.indeed.com/viewjob?jk=6553fe8d88b5cc2c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Consulting Associate/Full Stack Developer (Forensic Services practice)</t>
+          <t>Senior AWS Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Charles River Associates</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Scala, DynamoDB, Docker</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=853dfe0e00183c55</t>
+          <t>https://www.indeed.com/viewjob?jk=403a9d53356963ed</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Architecture Senior Advisor</t>
+          <t>Product Engineer II - Data Management</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd686e8a6d93c00</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5fcd43916fb352</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Architecture Senior Advisor</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a100c3ae58674b37</t>
+          <t>https://www.indeed.com/viewjob?jk=903ff22fdc58906d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Holtzbrinck Publishing Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6553fe8d88b5cc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2630a842cc6382</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403a9d53356963ed</t>
+          <t>https://www.indeed.com/viewjob?jk=c9cf0398eaa58c55</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer II - Surgery</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=443f2bd8cdbdcd91</t>
+          <t>https://www.indeed.com/viewjob?jk=16d25674f9943018</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9cf0398eaa58c55</t>
+          <t>https://www.indeed.com/viewjob?jk=709d2dc8e12638c5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Lyra Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Tableau, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d25674f9943018</t>
+          <t>https://www.indeed.com/viewjob?jk=c13b3570f31644de</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709d2dc8e12638c5</t>
+          <t>https://www.indeed.com/viewjob?jk=760e0caf358fa7ba</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Lyra Health</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Tableau, Terraform, Airflow</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c13b3570f31644de</t>
+          <t>https://www.indeed.com/viewjob?jk=06c0ec6191f51dd9</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=760e0caf358fa7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=4a46908cd0a69c52</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c0ec6191f51dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=2d887191c1e6747a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a46908cd0a69c52</t>
+          <t>https://www.indeed.com/viewjob?jk=24a63124749b1283</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d887191c1e6747a</t>
+          <t>https://www.indeed.com/viewjob?jk=9ef589b39c6904ab</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Full Stack AI + Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Techtorch</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Spark Streaming, Kafka, PostgreSQL, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6740052e5af1c2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae687a47012d375</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a63124749b1283</t>
+          <t>https://www.indeed.com/viewjob?jk=526789b5a039d9e4</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ef589b39c6904ab</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab868ce436a523f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer- Forward Deployed</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae687a47012d375</t>
+          <t>https://www.indeed.com/viewjob?jk=bda2c2b8bdd5703d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,42 +2586,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526789b5a039d9e4</t>
+          <t>https://www.indeed.com/viewjob?jk=c2be82c2c579e7f0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Radar</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, Vertex AI, Spark, Scala, Kafka, Dask, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab868ce436a523f</t>
+          <t>https://www.indeed.com/viewjob?jk=f34740da82b33461</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Constitution Surgery Alliance</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,102 +2666,102 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e91aba2a71eea06</t>
+          <t>https://www.indeed.com/viewjob?jk=8ceb9d089a51d56c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4df4e36af097a7</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6f76b9337a13b3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>Senior AI Platform Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2be82c2c579e7f0</t>
+          <t>https://www.indeed.com/viewjob?jk=16a9b21087d9070b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Forward Deployed</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,94 +2771,94 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda2c2b8bdd5703d</t>
+          <t>https://www.indeed.com/viewjob?jk=8383bcaf3f0d64cd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Kinsale Management Inc</t>
+          <t>BRUNT Workwear</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a938739108dd1870</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a66e52ac0ae1b3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>BRUNT Workwear</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>North Reading, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78902f746ba9d9e9</t>
+          <t>https://www.indeed.com/viewjob?jk=ed9ff440388b3f76</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Engineer II, AWS Connect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Radar</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Spark, Scala, Kafka, Dask, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34740da82b33461</t>
+          <t>https://www.indeed.com/viewjob?jk=3acabec1c779e4f7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Acquire-Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BehaviorSpan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ceb9d089a51d56c</t>
+          <t>https://www.indeed.com/viewjob?jk=a716d21991893978</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6f76b9337a13b3</t>
+          <t>https://www.indeed.com/viewjob?jk=4720246dd1e23d07</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer, Infrastructure</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a9b21087d9070b</t>
+          <t>https://www.indeed.com/viewjob?jk=010c395bdcd7a30d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8383bcaf3f0d64cd</t>
+          <t>https://www.indeed.com/viewjob?jk=f31a5af9350429b9</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BRUNT Workwear</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a66e52ac0ae1b3</t>
+          <t>https://www.indeed.com/viewjob?jk=5a1dc59f217f9fce</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BRUNT Workwear</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>North Reading, MA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed9ff440388b3f76</t>
+          <t>https://www.indeed.com/viewjob?jk=df60f817f0201540</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Engineer II, AWS Connect</t>
+          <t>Senior IT Analyst Applications</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3acabec1c779e4f7</t>
+          <t>https://www.indeed.com/viewjob?jk=16716305f57ba769</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Acquire-Site Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BehaviorSpan</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,19 +3156,19 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a716d21991893978</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6ec5c4dd06dea5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>Enlyte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010c395bdcd7a30d</t>
+          <t>https://www.indeed.com/viewjob?jk=623ad57a66a94f1a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Interra Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,112 +3216,112 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31a5af9350429b9</t>
+          <t>https://www.indeed.com/viewjob?jk=dffdb4bf979c0c04</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Newsbreak</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a1dc59f217f9fce</t>
+          <t>https://www.indeed.com/viewjob?jk=f967de110027227c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Azure Data Warehouse Architect</t>
+          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Newsbreak</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df60f817f0201540</t>
+          <t>https://www.indeed.com/viewjob?jk=ea855ad903dd71df</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Platform Engineering Architect - AI Automation</t>
+          <t>Customer Success Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Clarity Innovations, LLC</t>
+          <t>Mixpanel</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Jessup, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, ETL, dbt, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,67 +3331,67 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d32c274c61b107e</t>
+          <t>https://www.indeed.com/viewjob?jk=953ecd5971ae2bf1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6ec5c4dd06dea5</t>
+          <t>https://www.indeed.com/viewjob?jk=3fc83920e558138a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior IT Analyst Applications</t>
+          <t>Senior Software Engineer, App</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,67 +3401,67 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16716305f57ba769</t>
+          <t>https://www.indeed.com/viewjob?jk=c5acf07a00ef614c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>API Gateway, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623ad57a66a94f1a</t>
+          <t>https://www.indeed.com/viewjob?jk=a8dc47a59b46765c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Interra Health</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dffdb4bf979c0c04</t>
+          <t>https://www.indeed.com/viewjob?jk=ed909357965ec568</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Newsbreak</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f967de110027227c</t>
+          <t>https://www.indeed.com/viewjob?jk=a49347bb46652a75</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
+          <t>Instuctor , Cloud Computing &amp; Devops(CCDO)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Newsbreak</t>
+          <t>Fullstack Academy</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea855ad903dd71df</t>
+          <t>https://www.indeed.com/viewjob?jk=81ff13fcbdc21173</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,19 +3576,19 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877d45e3d1a625d6</t>
+          <t>https://www.indeed.com/viewjob?jk=5cf30157db81ea0e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Cloud Data Platform</t>
+          <t>Sr. Data Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>YETI</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Informatica PowerCenter, Data Modeling, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Vertex AI, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de80a4e1ea3c7456</t>
+          <t>https://www.indeed.com/viewjob?jk=6c9a108f2d63b6a3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Scientist Associate – Product, Experience and Technology (PXT) Analytics Team</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fc83920e558138a</t>
+          <t>https://www.indeed.com/viewjob?jk=e733ae2cd5148257</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, App</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Fortegra</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,532 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5acf07a00ef614c</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>MuleSoft/Python Software Engineer - OIT</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Emory University</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a511e772aaa75c08</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>API Gateway, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8dc47a59b46765c</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Business Informatics Support Data Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Trillium Health Resources</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed909357965ec568</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Business Informatics Support Data Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Trillium Health Resources</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a49347bb46652a75</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Instuctor , Cloud Computing &amp; Devops(CCDO)</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Fullstack Academy</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=81ff13fcbdc21173</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Software Architect – Manufacturing Test</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Cerebras Systems</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c04a9f371533f2c</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Software Architect – Manufacturing Test</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Cerebras Systems</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=132ec3a8e9018054</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Data Scientist Associate – Product, Experience and Technology (PXT) Analytics Team</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e733ae2cd5148257</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Sr. Data Architect</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>YETI</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Vertex AI, Scala, Databricks Lakehouse</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c9a108f2d63b6a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Nexstar Media Group, Inc.</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b532541851ceb06</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Pearson</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b8a567bdd35f252</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Truist</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5cf30157db81ea0e</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e70cddc4d406c6fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Junior AI Platform Engineer, Infrastrucure</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>accrete</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5496a0bc2b4bd3eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Data</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Lila Sciences</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e71383b94e86fbaa</t>
+          <t>https://www.indeed.com/viewjob?jk=a5720513548105a7</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-27.xlsx
+++ b/results/job_matches_2026-05-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,70 +468,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Forward Deployed Engineer - Data Migration &amp; Data Consolidation Platforms</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A-TEK Inc</t>
+          <t>Rackspace Technology</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.7</v>
+        <v>25</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle</t>
+          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdcddba2d97d56f1</t>
+          <t>https://www.indeed.com/viewjob?jk=b3063b040bfb390f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - Data Migration &amp; Data Consolidation Platforms</t>
+          <t>Senior Analytics Engineer, People Data</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rackspace Technology</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>22.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3063b040bfb390f</t>
+          <t>https://www.indeed.com/viewjob?jk=d5886aefde3a2ed5</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5886aefde3a2ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=392458a76ed6493b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, People Data</t>
+          <t>Enterprise Data Warehouse (EDW) ETL/Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>22.9</v>
+        <v>20.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, BigQuery, Spark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=392458a76ed6493b</t>
+          <t>https://www.indeed.com/viewjob?jk=2655650a85cb9fcd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse (EDW) ETL/Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2655650a85cb9fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=e069ef7a7b20f315</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Specialist Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e069ef7a7b20f315</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff097337c23c8bf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Specialist Software Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
+          <t>AWS, Glue, Lambda, S3, SNS, IAM, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff097337c23c8bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2c299fe3483f84e7</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Engineer – Data Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c81fd4cfc405e48</t>
+          <t>https://www.indeed.com/viewjob?jk=9cb5a838303cab7f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer – Data Engineering</t>
+          <t>DevOps Engineer – Data Engineering</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f642c610470a071</t>
+          <t>https://www.indeed.com/viewjob?jk=5c81fd4cfc405e48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer (in person)</t>
+          <t>Senior DevOps Engineer – Data Engineering</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SEP</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Westfield, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586f1008eb3dc860</t>
+          <t>https://www.indeed.com/viewjob?jk=7f642c610470a071</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (in person)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SEP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westfield, IN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, Redshift, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e523bf5a5bf5d62b</t>
+          <t>https://www.indeed.com/viewjob?jk=586f1008eb3dc860</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Engineering</t>
+          <t>Senior Software Engineer - Data Insights</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Roku</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ef9537310f7214</t>
+          <t>https://www.indeed.com/viewjob?jk=79537138cc31fdfa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer, I - Data Engineering</t>
+          <t>Senior Software Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TORC Robotics</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2976c8aa5f80420</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ef9537310f7214</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Software Engineer, I - Data Engineering</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2322ef59d1218d09</t>
+          <t>https://www.indeed.com/viewjob?jk=e2976c8aa5f80420</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Senior, Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Vertex AI, Scala, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=770d98b3f2c61a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=c3681d29da27c86c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Data Specialist</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Spark, PySpark, Scala, PostgreSQL, DataOps, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ddb8e746b2d111</t>
+          <t>https://www.indeed.com/viewjob?jk=2322ef59d1218d09</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2002a3bb054db4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=770d98b3f2c61a3f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>AI Data Specialist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Spark, PySpark, Scala, PostgreSQL, DataOps, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dae15109dd782046</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ddb8e746b2d111</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Java ReactJS AWS Developer Payments</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=213ccd9512c0c9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=2002a3bb054db4fd</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424703caefd6d113</t>
+          <t>https://www.indeed.com/viewjob?jk=dae15109dd782046</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java ReactJS AWS Developer Payments</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101061bea2a8593b</t>
+          <t>https://www.indeed.com/viewjob?jk=213ccd9512c0c9dc</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Modem Machine Learning Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3f6235da80ec1d</t>
+          <t>https://www.indeed.com/viewjob?jk=424703caefd6d113</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd094809bea2029</t>
+          <t>https://www.indeed.com/viewjob?jk=101061bea2a8593b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Back End Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Grand Circle Travel</t>
+          <t>Vanda Pharmaceuticals</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,59 +1476,59 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54baeed1bb9bcd57</t>
+          <t>https://www.indeed.com/viewjob?jk=94127b7cba7e23df</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pr AI Cloud Systems Engineer (RITM0479748)</t>
+          <t>Modem Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Discount Tire</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc9dfce7125ed878</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3f6235da80ec1d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Developer / Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Keystone Sports Construction</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phoenixville, PA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Azure, PostgreSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a62b9aa861f18b</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd094809bea2029</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Grand Circle Travel</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd51c65d58c91761</t>
+          <t>https://www.indeed.com/viewjob?jk=54baeed1bb9bcd57</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer - Product</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c6d1fd76fe3448</t>
+          <t>https://www.indeed.com/viewjob?jk=d76a9122ce202148</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Dot Net Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DNS Solutions Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c46f3131e66c1a54</t>
+          <t>https://www.indeed.com/viewjob?jk=771ada6d7a170a6d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Pr AI Cloud Systems Engineer (RITM0479748)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Quarterhill</t>
+          <t>Discount Tire</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,42 +1676,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ab23efc926ec48</t>
+          <t>https://www.indeed.com/viewjob?jk=dc9dfce7125ed878</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>DNS Solutions Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0a72f863d410844</t>
+          <t>https://www.indeed.com/viewjob?jk=c46f3131e66c1a54</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake, AWS)</t>
+          <t>Full Stack Developer / Cloud Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Keystone Sports Construction</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Phoenixville, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Time Travel, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Azure, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e3f82c93d576f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a62b9aa861f18b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62a0487a6b58cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=fd51c65d58c91761</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AWS Data Engineer (Cloud Data Platform &amp; Pipeline Specialist) (FTE / Onsite)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,59 +1826,59 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2feefef0c932976c</t>
+          <t>https://www.indeed.com/viewjob?jk=66c6d1fd76fe3448</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Full Stack Application Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Specialty Building Products</t>
+          <t>Quarterhill</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6435e356286a621f</t>
+          <t>https://www.indeed.com/viewjob?jk=87ab23efc926ec48</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Architecture Senior Advisor</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,42 +1886,42 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd686e8a6d93c00</t>
+          <t>https://www.indeed.com/viewjob?jk=a0a72f863d410844</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Holtzbrinck Publishing Group</t>
+          <t>OXIO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Kafka, Cassandra, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6553fe8d88b5cc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=f004fa27cdbd27bd</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer</t>
+          <t>Data Engineer (Snowflake, AWS)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Time Travel, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403a9d53356963ed</t>
+          <t>https://www.indeed.com/viewjob?jk=3e3f82c93d576f7a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Product Engineer II - Data Management</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Databricks, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5fcd43916fb352</t>
+          <t>https://www.indeed.com/viewjob?jk=e62a0487a6b58cf5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AWS Data Engineer (Cloud Data Platform &amp; Pipeline Specialist) (FTE / Onsite)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=903ff22fdc58906d</t>
+          <t>https://www.indeed.com/viewjob?jk=2feefef0c932976c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2630a842cc6382</t>
+          <t>https://www.indeed.com/viewjob?jk=e5bdaa12fae92021</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9cf0398eaa58c55</t>
+          <t>https://www.indeed.com/viewjob?jk=affa4e6360039969</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Senior Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Specialty Building Products</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d25674f9943018</t>
+          <t>https://www.indeed.com/viewjob?jk=6435e356286a621f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Holtzbrinck Publishing Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709d2dc8e12638c5</t>
+          <t>https://www.indeed.com/viewjob?jk=6553fe8d88b5cc2c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior AWS Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lyra Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Tableau, Terraform, Airflow</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c13b3570f31644de</t>
+          <t>https://www.indeed.com/viewjob?jk=403a9d53356963ed</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>National Carwash Solutions, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wells, ME, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=760e0caf358fa7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=7b93670fdfe811fb</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
+          <t>Product Engineer II - Data Management</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c0ec6191f51dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5fcd43916fb352</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a46908cd0a69c52</t>
+          <t>https://www.indeed.com/viewjob?jk=903ff22fdc58906d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d887191c1e6747a</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2630a842cc6382</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a63124749b1283</t>
+          <t>https://www.indeed.com/viewjob?jk=c9cf0398eaa58c55</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ef589b39c6904ab</t>
+          <t>https://www.indeed.com/viewjob?jk=16d25674f9943018</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae687a47012d375</t>
+          <t>https://www.indeed.com/viewjob?jk=709d2dc8e12638c5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Lyra Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Tableau, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526789b5a039d9e4</t>
+          <t>https://www.indeed.com/viewjob?jk=c13b3570f31644de</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab868ce436a523f</t>
+          <t>https://www.indeed.com/viewjob?jk=760e0caf358fa7ba</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Forward Deployed</t>
+          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda2c2b8bdd5703d</t>
+          <t>https://www.indeed.com/viewjob?jk=06c0ec6191f51dd9</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,42 +2586,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2be82c2c579e7f0</t>
+          <t>https://www.indeed.com/viewjob?jk=4a46908cd0a69c52</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Azure Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Radar</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Spark, Scala, Kafka, Dask, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34740da82b33461</t>
+          <t>https://www.indeed.com/viewjob?jk=2d887191c1e6747a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ceb9d089a51d56c</t>
+          <t>https://www.indeed.com/viewjob?jk=24a63124749b1283</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6f76b9337a13b3</t>
+          <t>https://www.indeed.com/viewjob?jk=9ef589b39c6904ab</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer, Infrastructure</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a9b21087d9070b</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae687a47012d375</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8383bcaf3f0d64cd</t>
+          <t>https://www.indeed.com/viewjob?jk=526789b5a039d9e4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BRUNT Workwear</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a66e52ac0ae1b3</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab868ce436a523f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer- Forward Deployed</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BRUNT Workwear</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>North Reading, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Data Modeling, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed9ff440388b3f76</t>
+          <t>https://www.indeed.com/viewjob?jk=bda2c2b8bdd5703d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Engineer II, AWS Connect</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3acabec1c779e4f7</t>
+          <t>https://www.indeed.com/viewjob?jk=c2be82c2c579e7f0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Acquire-Site Reliability Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BehaviorSpan</t>
+          <t>Radar</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Vertex AI, Spark, Scala, Kafka, Dask, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a716d21991893978</t>
+          <t>https://www.indeed.com/viewjob?jk=f34740da82b33461</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4720246dd1e23d07</t>
+          <t>https://www.indeed.com/viewjob?jk=8ceb9d089a51d56c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Scala, Kafka, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010c395bdcd7a30d</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6f76b9337a13b3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>DevOps Engineer V</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31a5af9350429b9</t>
+          <t>https://www.indeed.com/viewjob?jk=5e68650fbc89cc24</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Dallas College</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a1dc59f217f9fce</t>
+          <t>https://www.indeed.com/viewjob?jk=555365aa6be21a1c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Azure Data Warehouse Architect</t>
+          <t>Senior AI Platform Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df60f817f0201540</t>
+          <t>https://www.indeed.com/viewjob?jk=16a9b21087d9070b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior IT Analyst Applications</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16716305f57ba769</t>
+          <t>https://www.indeed.com/viewjob?jk=8383bcaf3f0d64cd</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>BRUNT Workwear</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6ec5c4dd06dea5</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a66e52ac0ae1b3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>BRUNT Workwear</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Reading, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623ad57a66a94f1a</t>
+          <t>https://www.indeed.com/viewjob?jk=ed9ff440388b3f76</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Engineer II, AWS Connect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Interra Health</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,102 +3226,102 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dffdb4bf979c0c04</t>
+          <t>https://www.indeed.com/viewjob?jk=3acabec1c779e4f7</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Newsbreak</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f967de110027227c</t>
+          <t>https://www.indeed.com/viewjob?jk=4720246dd1e23d07</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Newsbreak</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea855ad903dd71df</t>
+          <t>https://www.indeed.com/viewjob?jk=5a1dc59f217f9fce</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Customer Success Architect</t>
+          <t>Azure Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Mixpanel</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, ETL, dbt, Git</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=953ecd5971ae2bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=df60f817f0201540</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior IT Analyst Applications</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,102 +3366,102 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fc83920e558138a</t>
+          <t>https://www.indeed.com/viewjob?jk=16716305f57ba769</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, App</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5acf07a00ef614c</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6ec5c4dd06dea5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Enlyte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8dc47a59b46765c</t>
+          <t>https://www.indeed.com/viewjob?jk=623ad57a66a94f1a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Interra Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed909357965ec568</t>
+          <t>https://www.indeed.com/viewjob?jk=dffdb4bf979c0c04</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Newsbreak</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a49347bb46652a75</t>
+          <t>https://www.indeed.com/viewjob?jk=f967de110027227c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Instuctor , Cloud Computing &amp; Devops(CCDO)</t>
+          <t>Growth Intelligence Engineer (Ads &amp; Revenue)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Fullstack Academy</t>
+          <t>Newsbreak</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,29 +3531,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Databricks, BigQuery, Hive, Spark, PySpark, Scala, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ff13fcbdc21173</t>
+          <t>https://www.indeed.com/viewjob?jk=ea855ad903dd71df</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cf30157db81ea0e</t>
+          <t>https://www.indeed.com/viewjob?jk=b9cca8004915611a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>YETI</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Vertex AI, Scala, Databricks Lakehouse</t>
+          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c9a108f2d63b6a3</t>
+          <t>https://www.indeed.com/viewjob?jk=74971fc125810e95</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Scientist Associate – Product, Experience and Technology (PXT) Analytics Team</t>
+          <t>Customer Success Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mixpanel</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, ETL, dbt, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e733ae2cd5148257</t>
+          <t>https://www.indeed.com/viewjob?jk=953ecd5971ae2bf1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Managing Engineer , Database &amp; Platform - Remote</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Fortegra</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,15 +3671,435 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, MongoDB, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d30f4ab12fb26c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Data and Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SitelogIQ</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cefa075363914f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, App</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Lila Sciences</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5acf07a00ef614c</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>API Gateway, IAM, RDS, Azure, Scala, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8dc47a59b46765c</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Business Informatics Support Data Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Trillium Health Resources</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed909357965ec568</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Business Informatics Support Data Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Trillium Health Resources</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a49347bb46652a75</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Instuctor , Cloud Computing &amp; Devops(CCDO)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Fullstack Academy</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81ff13fcbdc21173</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>SAS Developer (with Admin Background)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e1d837eef2e008b</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Migration</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>MongoDB</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4cc849c83d3469f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cf30157db81ea0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Sr. Data Architect</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>YETI</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Vertex AI, Scala, Databricks Lakehouse</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c9a108f2d63b6a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Data Scientist Associate – Product, Experience and Technology (PXT) Analytics Team</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e733ae2cd5148257</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Fortegra</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a5720513548105a7</t>
         </is>
